--- a/data sheet.xlsx
+++ b/data sheet.xlsx
@@ -15,8 +15,8 @@
     <sheet name="Data Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Sheet'!$B$2:$J$107</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Data Sheet'!$B$2:$J$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Sheet'!$B$2:$K$107</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Data Sheet'!$B$2:$K$107</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="205">
   <si>
     <t>넘버링 = 같은제품 (같은 배합비 같은 색도값의 이름만 다른제품)</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1042,6 +1042,10 @@
   </si>
   <si>
     <t>26.05.14 기준변경 48 &gt; 50</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>공지사항</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1408,130 +1412,130 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1933,52 +1937,54 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q319"/>
+  <dimension ref="A1:R319"/>
   <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="21"/>
   <cols>
     <col min="1" max="1" width="4.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="4.5" style="55" customWidth="1"/>
-    <col min="3" max="3" width="47.5" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.69921875" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.69921875" style="31" customWidth="1"/>
-    <col min="6" max="9" width="8.69921875" style="19" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="148" style="32" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.5" style="1" customWidth="1"/>
-    <col min="12" max="12" width="47.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="3.8984375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="8.69921875" style="1"/>
-    <col min="16" max="16" width="10.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.8984375" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="8.69921875" style="1"/>
+    <col min="2" max="2" width="4.5" style="52" customWidth="1"/>
+    <col min="3" max="3" width="47.5" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.69921875" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.69921875" style="15" customWidth="1"/>
+    <col min="6" max="6" width="25.69921875" style="30" customWidth="1"/>
+    <col min="7" max="10" width="8.69921875" style="18" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="148" style="31" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.5" style="1" customWidth="1"/>
+    <col min="13" max="13" width="47.5" style="37" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.8984375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="8.69921875" style="1"/>
+    <col min="17" max="17" width="10.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.8984375" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="8.69921875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="21.6" thickBot="1">
+    <row r="1" spans="1:18" ht="21.6" thickBot="1">
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="1"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="4"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="5"/>
-      <c r="L1" s="6" t="s">
+      <c r="J1" s="1"/>
+      <c r="K1" s="5"/>
+      <c r="M1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="M1" s="7"/>
-      <c r="O1" s="8" t="s">
+      <c r="N1" s="7"/>
+      <c r="P1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="R1" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="21.6" thickBot="1">
+    <row r="2" spans="1:18" ht="21.6" thickBot="1">
       <c r="B2" s="9" t="s">
         <v>4</v>
       </c>
@@ -1988,49 +1994,53 @@
       <c r="D2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="F2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="G2" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="14" t="s">
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="K2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="M2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="N2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="O2" s="17" t="s">
+      <c r="P2" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="18" t="s">
+      <c r="Q2" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="Q2" s="19">
-        <f>COUNTIFS($E$3:$E$105, P2)</f>
+      <c r="R2" s="18">
+        <f>COUNTIFS($F$3:$F$105, Q2)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="21" customHeight="1">
-      <c r="B3" s="20">
+    <row r="3" spans="1:18" ht="21" customHeight="1">
+      <c r="B3" s="19">
         <v>1</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="21">
         <v>46</v>
       </c>
-      <c r="E3" s="23" t="str">
-        <f t="shared" ref="E3:E66" si="0">IF(D3&gt;=90, "Light",
+      <c r="E3" s="21"/>
+      <c r="F3" s="22" t="str">
+        <f t="shared" ref="F3:F66" si="0">IF(D3&gt;=90, "Light",
  IF(D3&gt;=80, "Cinnamon",
  IF(D3&gt;=70, "Medium",
  IF(D3&gt;=60, "High",
@@ -2040,1742 +2050,1801 @@
  "Italian")))))))</f>
         <v>Full City</v>
       </c>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="25"/>
-      <c r="L3" s="26" t="s">
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="24"/>
+      <c r="M3" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="M3" s="27">
+      <c r="N3" s="26">
         <v>50</v>
       </c>
-      <c r="O3" s="17" t="s">
+      <c r="P3" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="P3" s="28" t="s">
+      <c r="Q3" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="Q3" s="19">
-        <f>COUNTIFS($E$3:$E$105, P3)</f>
+      <c r="R3" s="18">
+        <f>COUNTIFS($F$3:$F$105, Q3)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="21" customHeight="1">
-      <c r="B4" s="20">
+    <row r="4" spans="1:18" ht="21" customHeight="1">
+      <c r="B4" s="19">
         <v>2</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="29">
         <v>55</v>
       </c>
-      <c r="E4" s="31" t="str">
+      <c r="E4" s="29"/>
+      <c r="F4" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="19" t="s">
+      <c r="G4" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="19">
+      <c r="J4" s="18">
         <v>225</v>
       </c>
-      <c r="L4" s="26" t="s">
+      <c r="M4" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="M4" s="27">
+      <c r="N4" s="26">
         <v>48</v>
       </c>
-      <c r="O4" s="17" t="s">
+      <c r="P4" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="P4" s="33" t="s">
+      <c r="Q4" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="Q4" s="19">
-        <f t="shared" ref="Q4:Q9" si="1">COUNTIFS($E$3:$E$105, P4)</f>
+      <c r="R4" s="18">
+        <f t="shared" ref="R4:R9" si="1">COUNTIFS($F$3:$F$105, Q4)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="21" customHeight="1">
-      <c r="B5" s="20">
+    <row r="5" spans="1:18" ht="21" customHeight="1">
+      <c r="B5" s="19">
         <v>3</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="29">
         <v>55</v>
       </c>
-      <c r="E5" s="31" t="str">
+      <c r="E5" s="29"/>
+      <c r="F5" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F5" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="19" t="s">
+      <c r="G5" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="19">
+      <c r="J5" s="18">
         <v>225</v>
       </c>
-      <c r="L5" s="26" t="s">
+      <c r="M5" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="27">
+      <c r="N5" s="26">
         <v>48</v>
       </c>
-      <c r="O5" s="17" t="s">
+      <c r="P5" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="P5" s="34" t="s">
+      <c r="Q5" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="Q5" s="19">
+      <c r="R5" s="18">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="21" customHeight="1">
-      <c r="B6" s="20">
+    <row r="6" spans="1:18" ht="21" customHeight="1">
+      <c r="B6" s="19">
         <v>4</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="29">
         <v>55</v>
       </c>
-      <c r="E6" s="31" t="str">
+      <c r="E6" s="29"/>
+      <c r="F6" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F6" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="19" t="s">
+      <c r="G6" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="19">
+      <c r="J6" s="18">
         <v>236</v>
       </c>
-      <c r="L6" s="26" t="s">
+      <c r="M6" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="M6" s="27">
+      <c r="N6" s="26">
         <v>50</v>
       </c>
-      <c r="O6" s="17" t="s">
+      <c r="P6" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="P6" s="35" t="s">
+      <c r="Q6" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="Q6" s="19">
+      <c r="R6" s="18">
         <f t="shared" si="1"/>
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="21" customHeight="1">
-      <c r="B7" s="20">
+    <row r="7" spans="1:18" ht="21" customHeight="1">
+      <c r="B7" s="19">
         <v>5</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="29">
         <v>55</v>
       </c>
-      <c r="E7" s="31" t="str">
+      <c r="E7" s="29"/>
+      <c r="F7" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="G7" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="H7" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="I7" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="19">
+      <c r="J7" s="18">
         <v>211</v>
       </c>
-      <c r="L7" s="26" t="s">
+      <c r="M7" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="M7" s="27">
+      <c r="N7" s="26">
         <v>51</v>
       </c>
-      <c r="O7" s="17" t="s">
+      <c r="P7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="P7" s="36" t="s">
+      <c r="Q7" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="Q7" s="19">
+      <c r="R7" s="18">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="21" customHeight="1">
-      <c r="A8" s="37"/>
-      <c r="B8" s="20">
+    <row r="8" spans="1:18" ht="21" customHeight="1">
+      <c r="A8" s="36"/>
+      <c r="B8" s="19">
         <v>6</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="29">
         <v>53</v>
       </c>
-      <c r="E8" s="31" t="str">
+      <c r="E8" s="29"/>
+      <c r="F8" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="G8" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="H8" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="I8" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="I8" s="19">
+      <c r="J8" s="18">
         <v>216</v>
       </c>
-      <c r="O8" s="17" t="s">
+      <c r="P8" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="P8" s="39" t="s">
+      <c r="Q8" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="Q8" s="19">
+      <c r="R8" s="18">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="21" customHeight="1">
-      <c r="B9" s="20">
+    <row r="9" spans="1:18" ht="21" customHeight="1">
+      <c r="B9" s="19">
         <v>7</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="29">
         <v>61</v>
       </c>
-      <c r="E9" s="31" t="str">
+      <c r="E9" s="29"/>
+      <c r="F9" s="30" t="str">
         <f t="shared" si="0"/>
         <v>High</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="G9" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="19" t="s">
+      <c r="H9" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="I9" s="19">
+      <c r="J9" s="18">
         <v>225</v>
       </c>
-      <c r="O9" s="17" t="s">
+      <c r="P9" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="P9" s="40" t="s">
+      <c r="Q9" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="Q9" s="19">
+      <c r="R9" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="21" customHeight="1">
-      <c r="A10" s="37"/>
-      <c r="B10" s="20">
+    <row r="10" spans="1:18" ht="21" customHeight="1">
+      <c r="A10" s="36"/>
+      <c r="B10" s="19">
         <v>8</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="42">
+      <c r="D10" s="41">
         <v>52</v>
       </c>
-      <c r="E10" s="31" t="str">
+      <c r="E10" s="41"/>
+      <c r="F10" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F10" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="19" t="s">
+      <c r="G10" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="19">
+      <c r="J10" s="18">
         <v>231</v>
       </c>
-      <c r="O10" s="43" t="s">
+      <c r="P10" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="P10" s="44"/>
-      <c r="Q10" s="19">
-        <f>SUM(Q2:Q9)</f>
+      <c r="Q10" s="55"/>
+      <c r="R10" s="18">
+        <f>SUM(R2:R9)</f>
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="21" customHeight="1">
-      <c r="B11" s="20">
+    <row r="11" spans="1:18" ht="21" customHeight="1">
+      <c r="B11" s="19">
         <v>9</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="29">
         <v>55</v>
       </c>
-      <c r="E11" s="31" t="str">
+      <c r="E11" s="29"/>
+      <c r="F11" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="G11" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11" s="19" t="s">
+      <c r="H11" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="I11" s="19">
+      <c r="J11" s="18">
         <v>235</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="21" customHeight="1">
-      <c r="B12" s="20">
+    <row r="12" spans="1:18" ht="21" customHeight="1">
+      <c r="B12" s="19">
         <v>10</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="29">
         <v>39</v>
       </c>
-      <c r="E12" s="31" t="str">
+      <c r="E12" s="29"/>
+      <c r="F12" s="30" t="str">
         <f t="shared" si="0"/>
         <v>French</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="G12" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="H12" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="H12" s="19" t="s">
+      <c r="I12" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="I12" s="19">
+      <c r="J12" s="18">
         <v>214</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="21" customHeight="1">
-      <c r="B13" s="20">
+    <row r="13" spans="1:18" ht="21" customHeight="1">
+      <c r="B13" s="19">
         <v>11</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="15">
         <v>63</v>
       </c>
-      <c r="E13" s="31" t="str">
+      <c r="F13" s="30" t="str">
         <f t="shared" si="0"/>
         <v>High</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="21" customHeight="1">
-      <c r="B14" s="20">
+    <row r="14" spans="1:18" ht="21" customHeight="1">
+      <c r="B14" s="19">
         <v>12</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="29">
         <v>59</v>
       </c>
-      <c r="E14" s="31" t="str">
+      <c r="E14" s="29"/>
+      <c r="F14" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="G14" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="G14" s="19" t="s">
+      <c r="H14" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="H14" s="19" t="s">
+      <c r="I14" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="I14" s="19">
+      <c r="J14" s="18">
         <v>212</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="21" customHeight="1">
-      <c r="B15" s="20">
+    <row r="15" spans="1:18" ht="21" customHeight="1">
+      <c r="B15" s="19">
         <v>13</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="29">
         <v>59</v>
       </c>
-      <c r="E15" s="31" t="str">
+      <c r="E15" s="29"/>
+      <c r="F15" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F15" s="19" t="s">
+      <c r="G15" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="G15" s="19" t="s">
+      <c r="H15" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="H15" s="19" t="s">
+      <c r="I15" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="I15" s="19">
+      <c r="J15" s="18">
         <v>210</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="21" customHeight="1">
-      <c r="B16" s="20">
+    <row r="16" spans="1:18" ht="21" customHeight="1">
+      <c r="B16" s="19">
         <v>14</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="29">
         <v>43</v>
       </c>
-      <c r="E16" s="31" t="str">
+      <c r="E16" s="29"/>
+      <c r="F16" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Full City</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="G16" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="H16" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="H16" s="19" t="s">
+      <c r="I16" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="I16" s="19">
+      <c r="J16" s="18">
         <v>206</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="B17" s="20">
+    <row r="17" spans="1:11" ht="21" customHeight="1">
+      <c r="B17" s="19">
         <v>15</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="29">
         <v>55</v>
       </c>
-      <c r="E17" s="31" t="str">
+      <c r="E17" s="29"/>
+      <c r="F17" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="G17" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="G17" s="19" t="s">
+      <c r="H17" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="H17" s="19" t="s">
+      <c r="I17" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="I17" s="19">
+      <c r="J17" s="18">
         <v>209</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="B18" s="20">
+    <row r="18" spans="1:11" ht="21" customHeight="1">
+      <c r="B18" s="19">
         <v>16</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="29">
         <v>76</v>
       </c>
-      <c r="E18" s="31" t="str">
+      <c r="E18" s="29"/>
+      <c r="F18" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Medium</v>
       </c>
-      <c r="F18" s="19" t="s">
+      <c r="G18" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="G18" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H18" s="19" t="s">
+      <c r="H18" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="I18" s="19">
+      <c r="J18" s="18">
         <v>225</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="21" customHeight="1">
-      <c r="B19" s="20">
+    <row r="19" spans="1:11" ht="21" customHeight="1">
+      <c r="B19" s="19">
         <v>17</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="29">
         <v>54</v>
       </c>
-      <c r="E19" s="31" t="str">
+      <c r="E19" s="29"/>
+      <c r="F19" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F19" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G19" s="19" t="s">
+      <c r="G19" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="H19" s="19" t="s">
+      <c r="I19" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="I19" s="19">
+      <c r="J19" s="18">
         <v>221</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="21" customHeight="1">
-      <c r="B20" s="20">
-        <v>18</v>
-      </c>
-      <c r="C20" s="29" t="s">
+    <row r="20" spans="1:11" ht="21" customHeight="1">
+      <c r="B20" s="19">
+        <v>18</v>
+      </c>
+      <c r="C20" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="29">
         <v>52</v>
       </c>
-      <c r="E20" s="31" t="str">
+      <c r="E20" s="29"/>
+      <c r="F20" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F20" s="19" t="s">
+      <c r="G20" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="G20" s="19" t="s">
+      <c r="H20" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="H20" s="19" t="s">
+      <c r="I20" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="I20" s="19">
+      <c r="J20" s="18">
         <v>207</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="21" customHeight="1">
-      <c r="B21" s="20">
+    <row r="21" spans="1:11" ht="21" customHeight="1">
+      <c r="B21" s="19">
         <v>19</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="15">
         <v>55</v>
       </c>
-      <c r="E21" s="31" t="str">
+      <c r="F21" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="21" customHeight="1">
-      <c r="B22" s="20">
+    <row r="22" spans="1:11" ht="21" customHeight="1">
+      <c r="B22" s="19">
         <v>20</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="29">
         <v>47</v>
       </c>
-      <c r="E22" s="31" t="str">
+      <c r="E22" s="29"/>
+      <c r="F22" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Full City</v>
       </c>
-      <c r="F22" s="19" t="s">
+      <c r="G22" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="G22" s="19" t="s">
+      <c r="H22" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="H22" s="19" t="s">
+      <c r="I22" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="I22" s="19">
+      <c r="J22" s="18">
         <v>208</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="21" customHeight="1">
-      <c r="B23" s="20">
+    <row r="23" spans="1:11" ht="21" customHeight="1">
+      <c r="B23" s="19">
         <v>21</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="D23" s="30">
+      <c r="D23" s="29">
         <v>50</v>
       </c>
-      <c r="E23" s="31" t="str">
+      <c r="E23" s="29"/>
+      <c r="F23" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="21" customHeight="1">
-      <c r="B24" s="20">
+    <row r="24" spans="1:11" ht="21" customHeight="1">
+      <c r="B24" s="19">
         <v>22</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="D24" s="30">
+      <c r="D24" s="29">
         <v>53</v>
       </c>
-      <c r="E24" s="31" t="str">
+      <c r="E24" s="29"/>
+      <c r="F24" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F24" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G24" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="21" customHeight="1">
-      <c r="B25" s="20">
+      <c r="G24" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" s="18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="21" customHeight="1">
+      <c r="B25" s="19">
         <v>23</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D25" s="29">
         <v>61</v>
       </c>
-      <c r="E25" s="31" t="str">
+      <c r="E25" s="29"/>
+      <c r="F25" s="30" t="str">
         <f t="shared" si="0"/>
         <v>High</v>
       </c>
-      <c r="F25" s="45" t="s">
+      <c r="G25" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="G25" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H25" s="19" t="s">
+      <c r="H25" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I25" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="I25" s="19">
+      <c r="J25" s="18">
         <v>220</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="21" customHeight="1">
-      <c r="B26" s="20">
+    <row r="26" spans="1:11" ht="21" customHeight="1">
+      <c r="B26" s="19">
         <v>24</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C26" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="D26" s="30">
+      <c r="D26" s="29">
         <v>52</v>
       </c>
-      <c r="E26" s="31" t="str">
+      <c r="E26" s="29"/>
+      <c r="F26" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="J26" s="46" t="s">
+      <c r="K26" s="43" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="21" customHeight="1">
-      <c r="B27" s="20">
+    <row r="27" spans="1:11" ht="21" customHeight="1">
+      <c r="B27" s="19">
         <v>25</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="29">
         <v>53</v>
       </c>
-      <c r="E27" s="31" t="str">
+      <c r="E27" s="29"/>
+      <c r="F27" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F27" s="19" t="s">
+      <c r="G27" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="G27" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H27" s="19" t="s">
+      <c r="H27" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I27" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="I27" s="19">
+      <c r="J27" s="18">
         <v>228</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="21" customHeight="1">
-      <c r="B28" s="20">
+    <row r="28" spans="1:11" ht="21" customHeight="1">
+      <c r="B28" s="19">
         <v>26</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="15">
         <v>40</v>
       </c>
-      <c r="E28" s="31" t="str">
+      <c r="F28" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Full City</v>
       </c>
-      <c r="J28" s="46" t="s">
+      <c r="K28" s="43" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="21" customHeight="1">
-      <c r="A29" s="37"/>
-      <c r="B29" s="20">
+    <row r="29" spans="1:11" ht="21" customHeight="1">
+      <c r="A29" s="36"/>
+      <c r="B29" s="19">
         <v>27</v>
       </c>
-      <c r="C29" s="29" t="s">
+      <c r="C29" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="D29" s="30">
+      <c r="D29" s="29">
         <v>58</v>
       </c>
-      <c r="E29" s="31" t="str">
+      <c r="E29" s="29"/>
+      <c r="F29" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F29" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G29" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H29" s="19" t="s">
+      <c r="G29" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H29" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I29" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="I29" s="19">
+      <c r="J29" s="18">
         <v>232</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="21" customHeight="1">
-      <c r="B30" s="20">
+    <row r="30" spans="1:11" ht="21" customHeight="1">
+      <c r="B30" s="19">
         <v>28</v>
       </c>
-      <c r="C30" s="29" t="s">
+      <c r="C30" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="D30" s="30">
+      <c r="D30" s="29">
         <v>58</v>
       </c>
-      <c r="E30" s="31" t="str">
+      <c r="E30" s="29"/>
+      <c r="F30" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F30" s="19" t="s">
+      <c r="G30" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="G30" s="19" t="s">
+      <c r="H30" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="H30" s="19" t="s">
+      <c r="I30" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="I30" s="19">
+      <c r="J30" s="18">
         <v>214</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="21" customHeight="1">
-      <c r="A31" s="37"/>
-      <c r="B31" s="20">
+    <row r="31" spans="1:11" ht="21" customHeight="1">
+      <c r="A31" s="36"/>
+      <c r="B31" s="19">
         <v>29</v>
       </c>
-      <c r="C31" s="29" t="s">
+      <c r="C31" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="D31" s="30">
+      <c r="D31" s="29">
         <v>52</v>
       </c>
-      <c r="E31" s="31" t="str">
+      <c r="E31" s="29"/>
+      <c r="F31" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F31" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G31" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H31" s="19" t="s">
+      <c r="G31" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H31" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I31" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="I31" s="19">
+      <c r="J31" s="18">
         <v>227</v>
       </c>
-      <c r="J31" s="46" t="s">
+      <c r="K31" s="43" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="21" customHeight="1">
-      <c r="A32" s="37"/>
-      <c r="B32" s="20">
+    <row r="32" spans="1:11" ht="21" customHeight="1">
+      <c r="A32" s="36"/>
+      <c r="B32" s="19">
         <v>30</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C32" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="D32" s="30">
+      <c r="D32" s="29">
         <v>57</v>
       </c>
-      <c r="E32" s="31" t="str">
+      <c r="E32" s="29"/>
+      <c r="F32" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
     </row>
-    <row r="33" spans="2:10" ht="21" customHeight="1">
-      <c r="B33" s="20">
+    <row r="33" spans="2:11" ht="21" customHeight="1">
+      <c r="B33" s="19">
         <v>31</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C33" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="D33" s="30">
+      <c r="D33" s="29">
         <v>57</v>
       </c>
-      <c r="E33" s="31" t="str">
+      <c r="E33" s="29"/>
+      <c r="F33" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F33" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G33" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H33" s="19" t="s">
+      <c r="G33" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H33" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I33" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="I33" s="19">
+      <c r="J33" s="18">
         <v>220</v>
       </c>
     </row>
-    <row r="34" spans="2:10" ht="21" customHeight="1">
-      <c r="B34" s="20">
+    <row r="34" spans="2:11" ht="21" customHeight="1">
+      <c r="B34" s="19">
         <v>32</v>
       </c>
-      <c r="C34" s="29" t="s">
+      <c r="C34" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="D34" s="30">
+      <c r="D34" s="29">
         <v>49</v>
       </c>
-      <c r="E34" s="31" t="str">
+      <c r="E34" s="29"/>
+      <c r="F34" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Full City</v>
       </c>
-      <c r="F34" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G34" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H34" s="19" t="s">
+      <c r="G34" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H34" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I34" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="I34" s="19">
+      <c r="J34" s="18">
         <v>225</v>
       </c>
     </row>
-    <row r="35" spans="2:10" ht="21" customHeight="1">
-      <c r="B35" s="20">
+    <row r="35" spans="2:11" ht="21" customHeight="1">
+      <c r="B35" s="19">
         <v>33</v>
       </c>
-      <c r="C35" s="29" t="s">
+      <c r="C35" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="D35" s="30">
+      <c r="D35" s="29">
         <v>49</v>
       </c>
-      <c r="E35" s="31" t="str">
+      <c r="E35" s="29"/>
+      <c r="F35" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Full City</v>
       </c>
-      <c r="F35" s="19" t="s">
+      <c r="G35" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G35" s="19" t="s">
+      <c r="H35" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="H35" s="19" t="s">
+      <c r="I35" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="I35" s="19">
+      <c r="J35" s="18">
         <v>212</v>
       </c>
     </row>
-    <row r="36" spans="2:10" ht="21" customHeight="1">
-      <c r="B36" s="20">
+    <row r="36" spans="2:11" ht="21" customHeight="1">
+      <c r="B36" s="19">
         <v>34</v>
       </c>
-      <c r="C36" s="29" t="s">
+      <c r="C36" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="D36" s="30">
+      <c r="D36" s="29">
         <v>52</v>
       </c>
-      <c r="E36" s="31" t="str">
+      <c r="E36" s="29"/>
+      <c r="F36" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F36" s="19" t="s">
+      <c r="G36" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G36" s="19" t="s">
+      <c r="H36" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="H36" s="19" t="s">
+      <c r="I36" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="I36" s="19">
+      <c r="J36" s="18">
         <v>212</v>
       </c>
     </row>
-    <row r="37" spans="2:10" ht="21" customHeight="1">
-      <c r="B37" s="20">
+    <row r="37" spans="2:11" ht="21" customHeight="1">
+      <c r="B37" s="19">
         <v>35</v>
       </c>
-      <c r="C37" s="29" t="s">
+      <c r="C37" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="D37" s="30">
+      <c r="D37" s="29">
         <v>48</v>
       </c>
-      <c r="E37" s="31" t="str">
+      <c r="E37" s="29"/>
+      <c r="F37" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Full City</v>
       </c>
-      <c r="F37" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G37" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H37" s="19" t="s">
+      <c r="G37" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H37" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="I37" s="19">
+      <c r="J37" s="18">
         <v>232</v>
       </c>
     </row>
-    <row r="38" spans="2:10" ht="21" customHeight="1">
-      <c r="B38" s="20">
+    <row r="38" spans="2:11" ht="21" customHeight="1">
+      <c r="B38" s="19">
         <v>36</v>
       </c>
-      <c r="C38" s="29" t="s">
+      <c r="C38" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="D38" s="30">
+      <c r="D38" s="29">
         <v>64</v>
       </c>
-      <c r="E38" s="31" t="str">
+      <c r="E38" s="29"/>
+      <c r="F38" s="30" t="str">
         <f t="shared" si="0"/>
         <v>High</v>
       </c>
-      <c r="F38" s="19" t="s">
+      <c r="G38" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="G38" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H38" s="19" t="s">
+      <c r="H38" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I38" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="I38" s="19">
+      <c r="J38" s="18">
         <v>227</v>
       </c>
     </row>
-    <row r="39" spans="2:10" ht="21" customHeight="1">
-      <c r="B39" s="20">
+    <row r="39" spans="2:11" ht="21" customHeight="1">
+      <c r="B39" s="19">
         <v>37</v>
       </c>
-      <c r="C39" s="29" t="s">
+      <c r="C39" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="D39" s="30">
+      <c r="D39" s="29">
         <v>65</v>
       </c>
-      <c r="E39" s="31" t="str">
+      <c r="E39" s="29"/>
+      <c r="F39" s="30" t="str">
         <f t="shared" si="0"/>
         <v>High</v>
       </c>
-      <c r="F39" s="19" t="s">
+      <c r="G39" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="G39" s="19" t="s">
+      <c r="H39" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="H39" s="19" t="s">
+      <c r="I39" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="I39" s="19">
+      <c r="J39" s="18">
         <v>216</v>
       </c>
     </row>
-    <row r="40" spans="2:10" ht="21" customHeight="1">
-      <c r="B40" s="20">
+    <row r="40" spans="2:11" ht="21" customHeight="1">
+      <c r="B40" s="19">
         <v>38</v>
       </c>
-      <c r="C40" s="29" t="s">
+      <c r="C40" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="D40" s="30">
+      <c r="D40" s="29">
         <v>67</v>
       </c>
-      <c r="E40" s="31" t="str">
+      <c r="E40" s="29"/>
+      <c r="F40" s="30" t="str">
         <f t="shared" si="0"/>
         <v>High</v>
       </c>
-      <c r="F40" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G40" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H40" s="19" t="s">
+      <c r="G40" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H40" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I40" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="I40" s="19">
+      <c r="J40" s="18">
         <v>225</v>
       </c>
     </row>
-    <row r="41" spans="2:10" ht="21" customHeight="1">
-      <c r="B41" s="20">
+    <row r="41" spans="2:11" ht="21" customHeight="1">
+      <c r="B41" s="19">
         <v>39</v>
       </c>
-      <c r="C41" s="29" t="s">
+      <c r="C41" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="30">
+      <c r="D41" s="29">
         <v>48</v>
       </c>
-      <c r="E41" s="31" t="str">
+      <c r="E41" s="29"/>
+      <c r="F41" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Full City</v>
       </c>
-      <c r="F41" s="19" t="s">
+      <c r="G41" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="G41" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H41" s="19" t="s">
+      <c r="H41" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I41" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="I41" s="19">
+      <c r="J41" s="18">
         <v>223</v>
       </c>
-      <c r="J41" s="46" t="s">
+      <c r="K41" s="43" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="42" spans="2:10" ht="21" customHeight="1">
-      <c r="B42" s="20">
+    <row r="42" spans="2:11" ht="21" customHeight="1">
+      <c r="B42" s="19">
         <v>40</v>
       </c>
-      <c r="C42" s="29" t="s">
+      <c r="C42" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="D42" s="30">
+      <c r="D42" s="29">
         <v>49</v>
       </c>
-      <c r="E42" s="31" t="str">
+      <c r="E42" s="29"/>
+      <c r="F42" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Full City</v>
       </c>
-      <c r="F42" s="19" t="s">
+      <c r="G42" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="G42" s="19" t="s">
+      <c r="H42" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="H42" s="19" t="s">
+      <c r="I42" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="I42" s="19">
+      <c r="J42" s="18">
         <v>208</v>
       </c>
     </row>
-    <row r="43" spans="2:10" ht="21" customHeight="1">
-      <c r="B43" s="20">
+    <row r="43" spans="2:11" ht="21" customHeight="1">
+      <c r="B43" s="19">
         <v>41</v>
       </c>
-      <c r="C43" s="29" t="s">
+      <c r="C43" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="D43" s="30">
+      <c r="D43" s="29">
         <v>50</v>
       </c>
-      <c r="E43" s="31" t="str">
+      <c r="E43" s="29"/>
+      <c r="F43" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F43" s="47" t="s">
+      <c r="G43" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="G43" s="48" t="s">
+      <c r="H43" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H43" s="48" t="s">
+      <c r="I43" s="45" t="s">
         <v>111</v>
       </c>
-      <c r="I43" s="19">
+      <c r="J43" s="18">
         <v>219</v>
       </c>
     </row>
-    <row r="44" spans="2:10" ht="21" customHeight="1">
-      <c r="B44" s="20">
+    <row r="44" spans="2:11" ht="21" customHeight="1">
+      <c r="B44" s="19">
         <v>42</v>
       </c>
-      <c r="C44" s="29" t="s">
+      <c r="C44" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="D44" s="16">
+      <c r="D44" s="15">
         <v>49</v>
       </c>
-      <c r="E44" s="31" t="str">
+      <c r="F44" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Full City</v>
       </c>
-      <c r="J44" s="46" t="s">
+      <c r="K44" s="43" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="45" spans="2:10" ht="21" customHeight="1">
-      <c r="B45" s="20">
+    <row r="45" spans="2:11" ht="21" customHeight="1">
+      <c r="B45" s="19">
         <v>43</v>
       </c>
-      <c r="C45" s="29" t="s">
+      <c r="C45" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="D45" s="30">
+      <c r="D45" s="29">
         <v>74</v>
       </c>
-      <c r="E45" s="31" t="str">
+      <c r="E45" s="29"/>
+      <c r="F45" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Medium</v>
       </c>
     </row>
-    <row r="46" spans="2:10" ht="21" customHeight="1">
-      <c r="B46" s="20">
+    <row r="46" spans="2:11" ht="21" customHeight="1">
+      <c r="B46" s="19">
         <v>44</v>
       </c>
-      <c r="C46" s="29" t="s">
+      <c r="C46" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="D46" s="16">
+      <c r="D46" s="15">
         <v>47</v>
       </c>
-      <c r="E46" s="31" t="str">
+      <c r="F46" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Full City</v>
       </c>
     </row>
-    <row r="47" spans="2:10" ht="21" customHeight="1">
-      <c r="B47" s="20">
+    <row r="47" spans="2:11" ht="21" customHeight="1">
+      <c r="B47" s="19">
         <v>45</v>
       </c>
-      <c r="C47" s="29" t="s">
+      <c r="C47" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="D47" s="30">
+      <c r="D47" s="29">
         <v>54</v>
       </c>
-      <c r="E47" s="31" t="str">
+      <c r="E47" s="29"/>
+      <c r="F47" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F47" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="G47" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="H47" s="49" t="s">
+      <c r="G47" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="H47" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="I47" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="I47" s="49">
+      <c r="J47" s="46">
         <v>228</v>
       </c>
     </row>
-    <row r="48" spans="2:10" ht="21" customHeight="1">
-      <c r="B48" s="20">
+    <row r="48" spans="2:11" ht="21" customHeight="1">
+      <c r="B48" s="19">
         <v>46</v>
       </c>
-      <c r="C48" s="29" t="s">
+      <c r="C48" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="D48" s="30">
+      <c r="D48" s="29">
         <v>68</v>
       </c>
-      <c r="E48" s="31" t="str">
+      <c r="E48" s="29"/>
+      <c r="F48" s="30" t="str">
         <f t="shared" si="0"/>
         <v>High</v>
       </c>
-      <c r="F48" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G48" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H48" s="19" t="s">
+      <c r="G48" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H48" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I48" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="I48" s="19">
+      <c r="J48" s="18">
         <v>228</v>
       </c>
     </row>
-    <row r="49" spans="2:10" ht="21" customHeight="1">
-      <c r="B49" s="20">
+    <row r="49" spans="2:11" ht="21" customHeight="1">
+      <c r="B49" s="19">
         <v>47</v>
       </c>
-      <c r="C49" s="29" t="s">
+      <c r="C49" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="D49" s="30">
+      <c r="D49" s="29">
         <v>65</v>
       </c>
-      <c r="E49" s="31" t="str">
+      <c r="E49" s="29"/>
+      <c r="F49" s="30" t="str">
         <f t="shared" si="0"/>
         <v>High</v>
       </c>
-      <c r="F49" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G49" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H49" s="19" t="s">
+      <c r="G49" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H49" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I49" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="I49" s="19">
+      <c r="J49" s="18">
         <v>223</v>
       </c>
     </row>
-    <row r="50" spans="2:10" ht="21" customHeight="1">
-      <c r="B50" s="20">
+    <row r="50" spans="2:11" ht="21" customHeight="1">
+      <c r="B50" s="19">
         <v>48</v>
       </c>
-      <c r="C50" s="29" t="s">
+      <c r="C50" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D50" s="30">
+      <c r="D50" s="29">
         <v>59</v>
       </c>
-      <c r="E50" s="31" t="str">
+      <c r="E50" s="29"/>
+      <c r="F50" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F50" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G50" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H50" s="19" t="s">
+      <c r="G50" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H50" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I50" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="I50" s="19">
+      <c r="J50" s="18">
         <v>228</v>
       </c>
     </row>
-    <row r="51" spans="2:10" ht="21" customHeight="1">
-      <c r="B51" s="20">
+    <row r="51" spans="2:11" ht="21" customHeight="1">
+      <c r="B51" s="19">
         <v>49</v>
       </c>
-      <c r="C51" s="15" t="s">
+      <c r="C51" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D51" s="30">
+      <c r="D51" s="29">
         <v>53</v>
       </c>
-      <c r="E51" s="31" t="str">
+      <c r="E51" s="29"/>
+      <c r="F51" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F51" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G51" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H51" s="19" t="s">
+      <c r="G51" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H51" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I51" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="I51" s="19">
+      <c r="J51" s="18">
         <v>232</v>
       </c>
-      <c r="J51" s="46" t="s">
+      <c r="K51" s="43" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="52" spans="2:10" ht="21" customHeight="1">
-      <c r="B52" s="20">
+    <row r="52" spans="2:11" ht="21" customHeight="1">
+      <c r="B52" s="19">
         <v>50</v>
       </c>
-      <c r="C52" s="29" t="s">
+      <c r="C52" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="D52" s="30">
+      <c r="D52" s="29">
         <v>59</v>
       </c>
-      <c r="E52" s="31" t="str">
+      <c r="E52" s="29"/>
+      <c r="F52" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F52" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G52" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="53" spans="2:10" ht="21" customHeight="1">
-      <c r="B53" s="20">
+      <c r="G52" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H52" s="18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" ht="21" customHeight="1">
+      <c r="B53" s="19">
         <v>51</v>
       </c>
-      <c r="C53" s="29" t="s">
+      <c r="C53" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="D53" s="30">
+      <c r="D53" s="29">
         <v>64</v>
       </c>
-      <c r="E53" s="31" t="str">
+      <c r="E53" s="29"/>
+      <c r="F53" s="30" t="str">
         <f t="shared" si="0"/>
         <v>High</v>
       </c>
-      <c r="F53" s="19" t="s">
+      <c r="G53" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G53" s="19" t="s">
+      <c r="H53" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="H53" s="19" t="s">
+      <c r="I53" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="I53" s="19">
+      <c r="J53" s="18">
         <v>224</v>
       </c>
     </row>
-    <row r="54" spans="2:10" ht="21" customHeight="1">
-      <c r="B54" s="20">
+    <row r="54" spans="2:11" ht="21" customHeight="1">
+      <c r="B54" s="19">
         <v>52</v>
       </c>
-      <c r="C54" s="29" t="s">
+      <c r="C54" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="D54" s="30">
+      <c r="D54" s="29">
         <v>55</v>
       </c>
-      <c r="E54" s="31" t="str">
+      <c r="E54" s="29"/>
+      <c r="F54" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F54" s="19" t="s">
+      <c r="G54" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G54" s="19" t="s">
+      <c r="H54" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="H54" s="19" t="s">
+      <c r="I54" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="I54" s="19">
+      <c r="J54" s="18">
         <v>216</v>
       </c>
     </row>
-    <row r="55" spans="2:10" ht="21" customHeight="1">
-      <c r="B55" s="20">
+    <row r="55" spans="2:11" ht="21" customHeight="1">
+      <c r="B55" s="19">
         <v>53</v>
       </c>
-      <c r="C55" s="29" t="s">
+      <c r="C55" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="D55" s="30">
+      <c r="D55" s="29">
         <v>67</v>
       </c>
-      <c r="E55" s="31" t="str">
+      <c r="E55" s="29"/>
+      <c r="F55" s="30" t="str">
         <f t="shared" si="0"/>
         <v>High</v>
       </c>
-      <c r="F55" s="19" t="s">
+      <c r="G55" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G55" s="19" t="s">
+      <c r="H55" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="H55" s="19" t="s">
+      <c r="I55" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="I55" s="19">
+      <c r="J55" s="18">
         <v>218</v>
       </c>
     </row>
-    <row r="56" spans="2:10" ht="21" customHeight="1">
-      <c r="B56" s="20">
+    <row r="56" spans="2:11" ht="21" customHeight="1">
+      <c r="B56" s="19">
         <v>54</v>
       </c>
-      <c r="C56" s="29" t="s">
+      <c r="C56" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="D56" s="30">
+      <c r="D56" s="29">
         <v>52</v>
       </c>
-      <c r="E56" s="31" t="str">
+      <c r="E56" s="29"/>
+      <c r="F56" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F56" s="19" t="s">
+      <c r="G56" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G56" s="19" t="s">
+      <c r="H56" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="H56" s="19" t="s">
+      <c r="I56" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="I56" s="19">
+      <c r="J56" s="18">
         <v>227</v>
       </c>
     </row>
-    <row r="57" spans="2:10" ht="21" customHeight="1">
-      <c r="B57" s="20">
+    <row r="57" spans="2:11" ht="21" customHeight="1">
+      <c r="B57" s="19">
         <v>55</v>
       </c>
-      <c r="C57" s="29" t="s">
+      <c r="C57" s="28" t="s">
         <v>133</v>
       </c>
-      <c r="D57" s="30">
+      <c r="D57" s="29">
         <v>56</v>
       </c>
-      <c r="E57" s="31" t="str">
+      <c r="E57" s="29"/>
+      <c r="F57" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F57" s="19" t="s">
+      <c r="G57" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G57" s="19" t="s">
+      <c r="H57" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="H57" s="19" t="s">
+      <c r="I57" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="I57" s="19">
+      <c r="J57" s="18">
         <v>213</v>
       </c>
     </row>
-    <row r="58" spans="2:10" ht="21" customHeight="1">
-      <c r="B58" s="20">
+    <row r="58" spans="2:11" ht="21" customHeight="1">
+      <c r="B58" s="19">
         <v>56</v>
       </c>
-      <c r="C58" s="29" t="s">
+      <c r="C58" s="28" t="s">
         <v>135</v>
       </c>
-      <c r="D58" s="30">
+      <c r="D58" s="29">
         <v>56</v>
       </c>
-      <c r="E58" s="31" t="str">
+      <c r="E58" s="29"/>
+      <c r="F58" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F58" s="19" t="s">
+      <c r="G58" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="G58" s="19" t="s">
+      <c r="H58" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="H58" s="19" t="s">
+      <c r="I58" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="I58" s="19">
+      <c r="J58" s="18">
         <v>214.5</v>
       </c>
     </row>
-    <row r="59" spans="2:10" ht="21" customHeight="1">
-      <c r="B59" s="20">
+    <row r="59" spans="2:11" ht="21" customHeight="1">
+      <c r="B59" s="19">
         <v>57</v>
       </c>
-      <c r="C59" s="29" t="s">
+      <c r="C59" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="D59" s="30">
+      <c r="D59" s="29">
         <v>54</v>
       </c>
-      <c r="E59" s="31" t="str">
+      <c r="E59" s="29"/>
+      <c r="F59" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F59" s="19" t="s">
+      <c r="G59" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G59" s="19" t="s">
+      <c r="H59" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="H59" s="19" t="s">
+      <c r="I59" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="I59" s="19">
+      <c r="J59" s="18">
         <v>215</v>
       </c>
     </row>
-    <row r="60" spans="2:10" ht="21" customHeight="1">
-      <c r="B60" s="20">
+    <row r="60" spans="2:11" ht="21" customHeight="1">
+      <c r="B60" s="19">
         <v>58</v>
       </c>
-      <c r="C60" s="29" t="s">
+      <c r="C60" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="D60" s="30">
+      <c r="D60" s="29">
         <v>51</v>
       </c>
-      <c r="E60" s="31" t="str">
+      <c r="E60" s="29"/>
+      <c r="F60" s="30" t="str">
         <f t="shared" si="0"/>
         <v>City</v>
       </c>
-      <c r="F60" s="19" t="s">
+      <c r="G60" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G60" s="19" t="s">
+      <c r="H60" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="H60" s="19" t="s">
+      <c r="I60" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="I60" s="19">
+      <c r="J60" s="18">
         <v>215</v>
       </c>
     </row>
-    <row r="61" spans="2:10" ht="21" customHeight="1">
-      <c r="B61" s="20">
+    <row r="61" spans="2:11" ht="21" customHeight="1">
+      <c r="B61" s="19">
         <v>59</v>
       </c>
-      <c r="C61" s="29" t="s">
+      <c r="C61" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="D61" s="30">
+      <c r="D61" s="29">
         <v>61</v>
       </c>
-      <c r="E61" s="31" t="str">
+      <c r="E61" s="29"/>
+      <c r="F61" s="30" t="str">
         <f t="shared" si="0"/>
         <v>High</v>
       </c>
-      <c r="F61" s="19" t="s">
+      <c r="G61" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G61" s="19" t="s">
+      <c r="H61" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="H61" s="19" t="s">
+      <c r="I61" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="I61" s="19">
+      <c r="J61" s="18">
         <v>214</v>
       </c>
     </row>
-    <row r="62" spans="2:10" ht="21" customHeight="1">
-      <c r="B62" s="20">
+    <row r="62" spans="2:11" ht="21" customHeight="1">
+      <c r="B62" s="19">
         <v>60</v>
       </c>
-      <c r="C62" s="29" t="s">
+      <c r="C62" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="D62" s="30">
+      <c r="D62" s="29">
         <v>69</v>
       </c>
-      <c r="E62" s="31" t="str">
+      <c r="E62" s="29"/>
+      <c r="F62" s="30" t="str">
         <f t="shared" si="0"/>
         <v>High</v>
       </c>
-      <c r="F62" s="19" t="s">
+      <c r="G62" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G62" s="19" t="s">
+      <c r="H62" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="H62" s="19" t="s">
+      <c r="I62" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="I62" s="19">
+      <c r="J62" s="18">
         <v>218</v>
       </c>
     </row>
-    <row r="63" spans="2:10" ht="21" customHeight="1">
-      <c r="B63" s="20">
+    <row r="63" spans="2:11" ht="21" customHeight="1">
+      <c r="B63" s="19">
         <v>61</v>
       </c>
-      <c r="C63" s="29" t="s">
+      <c r="C63" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="D63" s="30">
+      <c r="D63" s="29">
         <v>75</v>
       </c>
-      <c r="E63" s="31" t="str">
+      <c r="E63" s="29"/>
+      <c r="F63" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Medium</v>
       </c>
-      <c r="F63" s="19" t="s">
+      <c r="G63" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G63" s="19" t="s">
+      <c r="H63" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="H63" s="19" t="s">
+      <c r="I63" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="I63" s="19">
+      <c r="J63" s="18">
         <v>217</v>
       </c>
-      <c r="J63" s="46" t="s">
+      <c r="K63" s="43" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="64" spans="2:10" ht="21" customHeight="1">
-      <c r="B64" s="20">
+    <row r="64" spans="2:11" ht="21" customHeight="1">
+      <c r="B64" s="19">
         <v>62</v>
       </c>
-      <c r="C64" s="29" t="s">
+      <c r="C64" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="D64" s="30">
+      <c r="D64" s="29">
         <v>75</v>
       </c>
-      <c r="E64" s="31" t="str">
+      <c r="E64" s="29"/>
+      <c r="F64" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Medium</v>
       </c>
-      <c r="F64" s="19" t="s">
+      <c r="G64" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G64" s="19" t="s">
+      <c r="H64" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="H64" s="19" t="s">
+      <c r="I64" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="I64" s="19">
+      <c r="J64" s="18">
         <v>214</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="21" customHeight="1">
-      <c r="A65" s="50"/>
-      <c r="B65" s="20">
+    <row r="65" spans="1:11" ht="21" customHeight="1">
+      <c r="A65" s="47"/>
+      <c r="B65" s="19">
         <v>63</v>
       </c>
-      <c r="C65" s="29" t="s">
+      <c r="C65" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="D65" s="30">
+      <c r="D65" s="29">
         <v>76</v>
       </c>
-      <c r="E65" s="31" t="str">
+      <c r="E65" s="29"/>
+      <c r="F65" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Medium</v>
       </c>
-      <c r="F65" s="19" t="s">
+      <c r="G65" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="G65" s="19" t="s">
+      <c r="H65" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="H65" s="19" t="s">
+      <c r="I65" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="I65" s="19">
+      <c r="J65" s="18">
         <v>208</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="21" customHeight="1">
-      <c r="A66" s="37"/>
-      <c r="B66" s="20">
+    <row r="66" spans="1:11" ht="21" customHeight="1">
+      <c r="A66" s="36"/>
+      <c r="B66" s="19">
         <v>64</v>
       </c>
-      <c r="C66" s="29" t="s">
+      <c r="C66" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="D66" s="30">
+      <c r="D66" s="29">
         <v>74</v>
       </c>
-      <c r="E66" s="31" t="str">
+      <c r="E66" s="29"/>
+      <c r="F66" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Medium</v>
       </c>
-      <c r="F66" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G66" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H66" s="19" t="s">
+      <c r="G66" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H66" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I66" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="I66" s="19">
+      <c r="J66" s="18">
         <v>228</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="21" customHeight="1">
-      <c r="A67" s="37"/>
-      <c r="B67" s="20">
+    <row r="67" spans="1:11" ht="21" customHeight="1">
+      <c r="A67" s="36"/>
+      <c r="B67" s="19">
         <v>65</v>
       </c>
-      <c r="C67" s="29" t="s">
+      <c r="C67" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="D67" s="30">
+      <c r="D67" s="29">
         <v>74</v>
       </c>
-      <c r="E67" s="31" t="str">
-        <f t="shared" ref="E67:E130" si="2">IF(D67&gt;=90, "Light",
+      <c r="E67" s="29"/>
+      <c r="F67" s="30" t="str">
+        <f t="shared" ref="F67:F130" si="2">IF(D67&gt;=90, "Light",
  IF(D67&gt;=80, "Cinnamon",
  IF(D67&gt;=70, "Medium",
  IF(D67&gt;=60, "High",
@@ -3785,1177 +3854,1217 @@
  "Italian")))))))</f>
         <v>Medium</v>
       </c>
-      <c r="F67" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G67" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H67" s="19" t="s">
+      <c r="G67" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H67" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I67" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="I67" s="19">
+      <c r="J67" s="18">
         <v>223</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="21" customHeight="1">
-      <c r="B68" s="20">
+    <row r="68" spans="1:11" ht="21" customHeight="1">
+      <c r="B68" s="19">
         <v>66</v>
       </c>
-      <c r="C68" s="29" t="s">
+      <c r="C68" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="D68" s="30">
+      <c r="D68" s="29">
         <v>49</v>
       </c>
-      <c r="E68" s="31" t="str">
+      <c r="E68" s="29"/>
+      <c r="F68" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Full City</v>
       </c>
-      <c r="F68" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G68" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H68" s="19" t="s">
+      <c r="G68" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H68" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I68" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="I68" s="19">
+      <c r="J68" s="18">
         <v>230</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="21" customHeight="1">
-      <c r="B69" s="20">
+    <row r="69" spans="1:11" ht="21" customHeight="1">
+      <c r="B69" s="19">
         <v>67</v>
       </c>
-      <c r="C69" s="29" t="s">
+      <c r="C69" s="28" t="s">
         <v>150</v>
       </c>
-      <c r="D69" s="30">
+      <c r="D69" s="29">
         <v>79</v>
       </c>
-      <c r="E69" s="31" t="str">
+      <c r="E69" s="29"/>
+      <c r="F69" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Medium</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="21" customHeight="1">
-      <c r="A70" s="51"/>
-      <c r="B70" s="20">
+    <row r="70" spans="1:11" ht="21" customHeight="1">
+      <c r="A70" s="48"/>
+      <c r="B70" s="19">
         <v>68</v>
       </c>
-      <c r="C70" s="29" t="s">
+      <c r="C70" s="28" t="s">
         <v>151</v>
       </c>
-      <c r="D70" s="30">
+      <c r="D70" s="29">
         <v>85</v>
       </c>
-      <c r="E70" s="31" t="str">
+      <c r="E70" s="29"/>
+      <c r="F70" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Cinnamon</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="21" customHeight="1">
-      <c r="A71" s="51"/>
-      <c r="B71" s="20">
+    <row r="71" spans="1:11" ht="21" customHeight="1">
+      <c r="A71" s="48"/>
+      <c r="B71" s="19">
         <v>69</v>
       </c>
-      <c r="C71" s="29" t="s">
+      <c r="C71" s="28" t="s">
         <v>152</v>
       </c>
-      <c r="D71" s="30">
+      <c r="D71" s="29">
         <v>85</v>
       </c>
-      <c r="E71" s="31" t="str">
+      <c r="E71" s="29"/>
+      <c r="F71" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Cinnamon</v>
       </c>
-      <c r="F71" s="19" t="s">
+      <c r="G71" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="G71" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H71" s="19" t="s">
+      <c r="H71" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I71" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="I71" s="19">
+      <c r="J71" s="18">
         <v>234</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="21" customHeight="1">
-      <c r="B72" s="20">
+    <row r="72" spans="1:11" ht="21" customHeight="1">
+      <c r="B72" s="19">
         <v>70</v>
       </c>
-      <c r="C72" s="29" t="s">
+      <c r="C72" s="28" t="s">
         <v>153</v>
       </c>
-      <c r="D72" s="30">
+      <c r="D72" s="29">
         <v>57</v>
       </c>
-      <c r="E72" s="31" t="str">
+      <c r="E72" s="29"/>
+      <c r="F72" s="30" t="str">
         <f t="shared" si="2"/>
         <v>City</v>
       </c>
-      <c r="F72" s="19" t="s">
+      <c r="G72" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="G72" s="19" t="s">
+      <c r="H72" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="H72" s="19" t="s">
+      <c r="I72" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="I72" s="19">
+      <c r="J72" s="18">
         <v>230</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="21" customHeight="1">
-      <c r="B73" s="20">
+    <row r="73" spans="1:11" ht="21" customHeight="1">
+      <c r="B73" s="19">
         <v>71</v>
       </c>
-      <c r="C73" s="29" t="s">
+      <c r="C73" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="D73" s="30">
+      <c r="D73" s="29">
         <v>63</v>
       </c>
-      <c r="E73" s="31" t="str">
+      <c r="E73" s="29"/>
+      <c r="F73" s="30" t="str">
         <f t="shared" si="2"/>
         <v>High</v>
       </c>
-      <c r="F73" s="19" t="s">
+      <c r="G73" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="G73" s="19" t="s">
+      <c r="H73" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="H73" s="19" t="s">
+      <c r="I73" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="I73" s="19">
+      <c r="J73" s="18">
         <v>216.5</v>
       </c>
-      <c r="J73" s="46" t="s">
+      <c r="K73" s="43" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="21" customHeight="1">
-      <c r="B74" s="20">
+    <row r="74" spans="1:11" ht="21" customHeight="1">
+      <c r="B74" s="19">
         <v>72</v>
       </c>
-      <c r="C74" s="29" t="s">
+      <c r="C74" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="D74" s="30">
+      <c r="D74" s="29">
         <v>48</v>
       </c>
-      <c r="E74" s="31" t="str">
+      <c r="E74" s="29"/>
+      <c r="F74" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Full City</v>
       </c>
-      <c r="J74" s="46" t="s">
+      <c r="K74" s="43" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="21" customHeight="1">
-      <c r="B75" s="20">
+    <row r="75" spans="1:11" ht="21" customHeight="1">
+      <c r="B75" s="19">
         <v>73</v>
       </c>
-      <c r="C75" s="29" t="s">
+      <c r="C75" s="28" t="s">
         <v>158</v>
       </c>
-      <c r="D75" s="30">
+      <c r="D75" s="29">
         <v>51</v>
       </c>
-      <c r="E75" s="31" t="str">
+      <c r="E75" s="29"/>
+      <c r="F75" s="30" t="str">
         <f t="shared" si="2"/>
         <v>City</v>
       </c>
-      <c r="F75" s="19" t="s">
+      <c r="G75" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="G75" s="19" t="s">
+      <c r="H75" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="H75" s="19" t="s">
+      <c r="I75" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="I75" s="19">
+      <c r="J75" s="18">
         <v>210</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="21" customHeight="1">
-      <c r="B76" s="20">
+    <row r="76" spans="1:11" ht="21" customHeight="1">
+      <c r="B76" s="19">
         <v>74</v>
       </c>
-      <c r="C76" s="29" t="s">
+      <c r="C76" s="28" t="s">
         <v>160</v>
       </c>
-      <c r="D76" s="30">
+      <c r="D76" s="29">
         <v>55</v>
       </c>
-      <c r="E76" s="31" t="str">
+      <c r="E76" s="29"/>
+      <c r="F76" s="30" t="str">
         <f t="shared" si="2"/>
         <v>City</v>
       </c>
-      <c r="F76" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G76" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H76" s="19" t="s">
+      <c r="G76" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H76" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I76" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="I76" s="19">
+      <c r="J76" s="18">
         <v>221</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="21" customHeight="1">
-      <c r="B77" s="20">
+    <row r="77" spans="1:11" ht="21" customHeight="1">
+      <c r="B77" s="19">
         <v>75</v>
       </c>
-      <c r="C77" s="29" t="s">
+      <c r="C77" s="28" t="s">
         <v>161</v>
       </c>
-      <c r="D77" s="30">
+      <c r="D77" s="29">
         <v>57</v>
       </c>
-      <c r="E77" s="31" t="str">
+      <c r="E77" s="29"/>
+      <c r="F77" s="30" t="str">
         <f t="shared" si="2"/>
         <v>City</v>
       </c>
-      <c r="F77" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G77" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H77" s="19" t="s">
+      <c r="G77" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H77" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I77" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="I77" s="19">
+      <c r="J77" s="18">
         <v>223</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="21" customHeight="1">
-      <c r="B78" s="20">
+    <row r="78" spans="1:11" ht="21" customHeight="1">
+      <c r="B78" s="19">
         <v>76</v>
       </c>
-      <c r="C78" s="29" t="s">
+      <c r="C78" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="D78" s="30">
+      <c r="D78" s="29">
         <v>61</v>
       </c>
-      <c r="E78" s="31" t="str">
+      <c r="E78" s="29"/>
+      <c r="F78" s="30" t="str">
         <f t="shared" si="2"/>
         <v>High</v>
       </c>
-      <c r="F78" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G78" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H78" s="19" t="s">
+      <c r="G78" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H78" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I78" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="I78" s="19">
+      <c r="J78" s="18">
         <v>231</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="21" customHeight="1">
-      <c r="B79" s="20">
+    <row r="79" spans="1:11" ht="21" customHeight="1">
+      <c r="B79" s="19">
         <v>77</v>
       </c>
-      <c r="C79" s="29" t="s">
+      <c r="C79" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="D79" s="30">
+      <c r="D79" s="29">
         <v>54</v>
       </c>
-      <c r="E79" s="31" t="str">
+      <c r="E79" s="29"/>
+      <c r="F79" s="30" t="str">
         <f t="shared" si="2"/>
         <v>City</v>
       </c>
-      <c r="F79" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G79" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H79" s="19" t="s">
+      <c r="G79" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H79" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I79" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="I79" s="19">
+      <c r="J79" s="18">
         <v>223</v>
       </c>
-      <c r="J79" s="46" t="s">
+      <c r="K79" s="43" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="21" customHeight="1">
-      <c r="B80" s="20">
+    <row r="80" spans="1:11" ht="21" customHeight="1">
+      <c r="B80" s="19">
         <v>78</v>
       </c>
-      <c r="C80" s="29" t="s">
+      <c r="C80" s="28" t="s">
         <v>165</v>
       </c>
-      <c r="D80" s="30">
+      <c r="D80" s="29">
         <v>54</v>
       </c>
-      <c r="E80" s="31" t="str">
+      <c r="E80" s="29"/>
+      <c r="F80" s="30" t="str">
         <f t="shared" si="2"/>
         <v>City</v>
       </c>
-      <c r="F80" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G80" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H80" s="19" t="s">
+      <c r="G80" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H80" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I80" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="I80" s="19">
+      <c r="J80" s="18">
         <v>231</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="21" customHeight="1">
-      <c r="B81" s="20">
+    <row r="81" spans="1:11" ht="21" customHeight="1">
+      <c r="B81" s="19">
         <v>79</v>
       </c>
-      <c r="C81" s="29" t="s">
+      <c r="C81" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="D81" s="30">
+      <c r="D81" s="29">
         <v>51</v>
       </c>
-      <c r="E81" s="31" t="str">
+      <c r="E81" s="29"/>
+      <c r="F81" s="30" t="str">
         <f t="shared" si="2"/>
         <v>City</v>
       </c>
-      <c r="F81" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G81" s="19" t="s">
+      <c r="G81" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H81" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="H81" s="19" t="s">
+      <c r="I81" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="I81" s="19">
+      <c r="J81" s="18">
         <v>225</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="21" customHeight="1">
-      <c r="A82" s="37"/>
-      <c r="B82" s="20">
+    <row r="82" spans="1:11" ht="21" customHeight="1">
+      <c r="A82" s="36"/>
+      <c r="B82" s="19">
         <v>80</v>
       </c>
-      <c r="C82" s="29" t="s">
+      <c r="C82" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="D82" s="30">
+      <c r="D82" s="29">
         <v>57</v>
       </c>
-      <c r="E82" s="31" t="str">
+      <c r="E82" s="29"/>
+      <c r="F82" s="30" t="str">
         <f t="shared" si="2"/>
         <v>City</v>
       </c>
-      <c r="F82" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G82" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H82" s="19" t="s">
+      <c r="G82" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H82" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I82" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="I82" s="19">
+      <c r="J82" s="18">
         <v>223</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="21" customHeight="1">
-      <c r="A83" s="37"/>
-      <c r="B83" s="20">
+    <row r="83" spans="1:11" ht="21" customHeight="1">
+      <c r="A83" s="36"/>
+      <c r="B83" s="19">
         <v>81</v>
       </c>
-      <c r="C83" s="29" t="s">
+      <c r="C83" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="D83" s="30">
+      <c r="D83" s="29">
         <v>53</v>
       </c>
-      <c r="E83" s="31" t="str">
+      <c r="E83" s="29"/>
+      <c r="F83" s="30" t="str">
         <f t="shared" si="2"/>
         <v>City</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="21" customHeight="1">
-      <c r="B84" s="20">
+    <row r="84" spans="1:11" ht="21" customHeight="1">
+      <c r="B84" s="19">
         <v>82</v>
       </c>
-      <c r="C84" s="29" t="s">
+      <c r="C84" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="D84" s="30">
+      <c r="D84" s="29">
         <v>64</v>
       </c>
-      <c r="E84" s="31" t="str">
+      <c r="E84" s="29"/>
+      <c r="F84" s="30" t="str">
         <f t="shared" si="2"/>
         <v>High</v>
       </c>
-      <c r="F84" s="52"/>
-      <c r="G84" s="52"/>
-      <c r="H84" s="52"/>
-      <c r="I84" s="52"/>
-    </row>
-    <row r="85" spans="1:10" ht="21" customHeight="1">
-      <c r="A85" s="37"/>
-      <c r="B85" s="20">
+      <c r="G84" s="49"/>
+      <c r="H84" s="49"/>
+      <c r="I84" s="49"/>
+      <c r="J84" s="49"/>
+    </row>
+    <row r="85" spans="1:11" ht="21" customHeight="1">
+      <c r="A85" s="36"/>
+      <c r="B85" s="19">
         <v>83</v>
       </c>
-      <c r="C85" s="29" t="s">
+      <c r="C85" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="D85" s="30">
+      <c r="D85" s="29">
         <v>58</v>
       </c>
-      <c r="E85" s="31" t="str">
+      <c r="E85" s="29"/>
+      <c r="F85" s="30" t="str">
         <f t="shared" si="2"/>
         <v>City</v>
       </c>
-      <c r="F85" s="52"/>
-      <c r="G85" s="52"/>
-      <c r="H85" s="52"/>
-      <c r="I85" s="52"/>
-    </row>
-    <row r="86" spans="1:10" ht="21" customHeight="1">
-      <c r="B86" s="20">
+      <c r="G85" s="49"/>
+      <c r="H85" s="49"/>
+      <c r="I85" s="49"/>
+      <c r="J85" s="49"/>
+    </row>
+    <row r="86" spans="1:11" ht="21" customHeight="1">
+      <c r="B86" s="19">
         <v>84</v>
       </c>
-      <c r="C86" s="29" t="s">
+      <c r="C86" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="D86" s="30">
+      <c r="D86" s="29">
         <v>60</v>
       </c>
-      <c r="E86" s="31" t="str">
+      <c r="E86" s="29"/>
+      <c r="F86" s="30" t="str">
         <f t="shared" si="2"/>
         <v>High</v>
       </c>
-      <c r="F86" s="19" t="s">
+      <c r="G86" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="G86" s="19" t="s">
+      <c r="H86" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="H86" s="19" t="s">
+      <c r="I86" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="I86" s="19">
+      <c r="J86" s="18">
         <v>207</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="21" customHeight="1">
-      <c r="B87" s="20">
+    <row r="87" spans="1:11" ht="21" customHeight="1">
+      <c r="B87" s="19">
         <v>85</v>
       </c>
-      <c r="C87" s="29" t="s">
+      <c r="C87" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="D87" s="30">
+      <c r="D87" s="29">
         <v>45</v>
       </c>
-      <c r="E87" s="31" t="str">
+      <c r="E87" s="29"/>
+      <c r="F87" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Full City</v>
       </c>
-      <c r="F87" s="19" t="s">
+      <c r="G87" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="G87" s="19" t="s">
+      <c r="H87" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="H87" s="19" t="s">
+      <c r="I87" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="I87" s="19">
+      <c r="J87" s="18">
         <v>199</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="21" customHeight="1">
-      <c r="B88" s="20">
+    <row r="88" spans="1:11" ht="21" customHeight="1">
+      <c r="B88" s="19">
         <v>86</v>
       </c>
-      <c r="C88" s="29" t="s">
+      <c r="C88" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="D88" s="30">
+      <c r="D88" s="29">
         <v>54</v>
       </c>
-      <c r="E88" s="31" t="str">
+      <c r="E88" s="29"/>
+      <c r="F88" s="30" t="str">
         <f t="shared" si="2"/>
         <v>City</v>
       </c>
-      <c r="F88" s="19" t="s">
+      <c r="G88" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="G88" s="19" t="s">
+      <c r="H88" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="H88" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="I88" s="19">
+      <c r="I88" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J88" s="18">
         <v>219</v>
       </c>
-      <c r="J88" s="46" t="s">
+      <c r="K88" s="43" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="21" customHeight="1">
-      <c r="B89" s="20">
+    <row r="89" spans="1:11" ht="21" customHeight="1">
+      <c r="B89" s="19">
         <v>87</v>
       </c>
-      <c r="C89" s="29" t="s">
+      <c r="C89" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="D89" s="30">
+      <c r="D89" s="29">
         <v>45</v>
       </c>
-      <c r="E89" s="31" t="str">
+      <c r="E89" s="29"/>
+      <c r="F89" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Full City</v>
       </c>
-      <c r="F89" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G89" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H89" s="19" t="s">
+      <c r="G89" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H89" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I89" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="I89" s="19">
+      <c r="J89" s="18">
         <v>230</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="21" customHeight="1">
-      <c r="B90" s="20">
+    <row r="90" spans="1:11" ht="21" customHeight="1">
+      <c r="B90" s="19">
         <v>88</v>
       </c>
-      <c r="C90" s="29" t="s">
+      <c r="C90" s="28" t="s">
         <v>179</v>
       </c>
-      <c r="D90" s="30">
+      <c r="D90" s="29">
         <v>60</v>
       </c>
-      <c r="E90" s="31" t="str">
+      <c r="E90" s="29"/>
+      <c r="F90" s="30" t="str">
         <f t="shared" si="2"/>
         <v>High</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="21" customHeight="1">
-      <c r="B91" s="20">
+    <row r="91" spans="1:11" ht="21" customHeight="1">
+      <c r="B91" s="19">
         <v>89</v>
       </c>
-      <c r="C91" s="29" t="s">
+      <c r="C91" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="D91" s="30">
+      <c r="D91" s="29">
         <v>45</v>
       </c>
-      <c r="E91" s="31" t="str">
+      <c r="E91" s="29"/>
+      <c r="F91" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Full City</v>
       </c>
-      <c r="F91" s="19" t="s">
+      <c r="G91" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="G91" s="19" t="s">
+      <c r="H91" s="18" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="21" customHeight="1">
-      <c r="B92" s="20">
+    <row r="92" spans="1:11" ht="21" customHeight="1">
+      <c r="B92" s="19">
         <v>90</v>
       </c>
-      <c r="C92" s="41" t="s">
+      <c r="C92" s="40" t="s">
         <v>181</v>
       </c>
-      <c r="D92" s="42">
+      <c r="D92" s="41">
         <v>45</v>
       </c>
-      <c r="E92" s="31" t="str">
+      <c r="E92" s="41"/>
+      <c r="F92" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Full City</v>
       </c>
-      <c r="F92" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G92" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H92" s="19" t="s">
+      <c r="G92" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H92" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I92" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="I92" s="19">
+      <c r="J92" s="18">
         <v>234</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="21" customHeight="1">
-      <c r="B93" s="20">
+    <row r="93" spans="1:11" ht="21" customHeight="1">
+      <c r="B93" s="19">
         <v>91</v>
       </c>
-      <c r="C93" s="29" t="s">
+      <c r="C93" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="D93" s="30">
+      <c r="D93" s="29">
         <v>60</v>
       </c>
-      <c r="E93" s="31" t="str">
+      <c r="E93" s="29"/>
+      <c r="F93" s="30" t="str">
         <f t="shared" si="2"/>
         <v>High</v>
       </c>
-      <c r="F93" s="19" t="s">
+      <c r="G93" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="G93" s="19" t="s">
+      <c r="H93" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="H93" s="19" t="s">
+      <c r="I93" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="I93" s="19">
+      <c r="J93" s="18">
         <v>208</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="21" customHeight="1">
-      <c r="B94" s="20">
+    <row r="94" spans="1:11" ht="21" customHeight="1">
+      <c r="B94" s="19">
         <v>92</v>
       </c>
-      <c r="C94" s="29" t="s">
+      <c r="C94" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="D94" s="30">
+      <c r="D94" s="29">
         <v>60</v>
       </c>
-      <c r="E94" s="31" t="str">
+      <c r="E94" s="29"/>
+      <c r="F94" s="30" t="str">
         <f t="shared" si="2"/>
         <v>High</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="21" customHeight="1">
-      <c r="B95" s="20">
+    <row r="95" spans="1:11" ht="21" customHeight="1">
+      <c r="B95" s="19">
         <v>93</v>
       </c>
-      <c r="C95" s="29" t="s">
+      <c r="C95" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="D95" s="30">
+      <c r="D95" s="29">
         <v>60</v>
       </c>
-      <c r="E95" s="31" t="str">
+      <c r="E95" s="29"/>
+      <c r="F95" s="30" t="str">
         <f t="shared" si="2"/>
         <v>High</v>
       </c>
-      <c r="F95" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G95" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" ht="21" customHeight="1">
-      <c r="B96" s="20">
+      <c r="G95" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H95" s="18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" ht="21" customHeight="1">
+      <c r="B96" s="19">
         <v>94</v>
       </c>
-      <c r="C96" s="29" t="s">
+      <c r="C96" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="D96" s="30">
+      <c r="D96" s="29">
         <v>47</v>
       </c>
-      <c r="E96" s="31" t="str">
+      <c r="E96" s="29"/>
+      <c r="F96" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Full City</v>
       </c>
-      <c r="F96" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G96" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H96" s="19" t="s">
+      <c r="G96" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H96" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I96" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="I96" s="19">
+      <c r="J96" s="18">
         <v>218</v>
       </c>
     </row>
-    <row r="97" spans="2:10" ht="21" customHeight="1">
-      <c r="B97" s="20">
+    <row r="97" spans="2:11" ht="21" customHeight="1">
+      <c r="B97" s="19">
         <v>95</v>
       </c>
-      <c r="C97" s="29" t="s">
+      <c r="C97" s="28" t="s">
         <v>186</v>
       </c>
-      <c r="D97" s="30">
+      <c r="D97" s="29">
         <v>55</v>
       </c>
-      <c r="E97" s="31" t="str">
+      <c r="E97" s="29"/>
+      <c r="F97" s="30" t="str">
         <f t="shared" si="2"/>
         <v>City</v>
       </c>
-      <c r="F97" s="19" t="s">
+      <c r="G97" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G97" s="19" t="s">
+      <c r="H97" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="H97" s="19" t="s">
+      <c r="I97" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="I97" s="19">
+      <c r="J97" s="18">
         <v>212</v>
       </c>
     </row>
-    <row r="98" spans="2:10" ht="21" customHeight="1">
-      <c r="B98" s="20">
+    <row r="98" spans="2:11" ht="21" customHeight="1">
+      <c r="B98" s="19">
         <v>96</v>
       </c>
-      <c r="C98" s="53" t="s">
+      <c r="C98" s="50" t="s">
         <v>187</v>
       </c>
-      <c r="D98" s="30">
+      <c r="D98" s="29">
         <v>53</v>
       </c>
-      <c r="E98" s="31" t="str">
+      <c r="E98" s="29"/>
+      <c r="F98" s="30" t="str">
         <f t="shared" si="2"/>
         <v>City</v>
       </c>
-      <c r="F98" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G98" s="19" t="s">
+      <c r="G98" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H98" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="H98" s="19" t="s">
+      <c r="I98" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="I98" s="19">
+      <c r="J98" s="18">
         <v>231</v>
       </c>
     </row>
-    <row r="99" spans="2:10" ht="21" customHeight="1">
-      <c r="B99" s="20">
+    <row r="99" spans="2:11" ht="21" customHeight="1">
+      <c r="B99" s="19">
         <v>97</v>
       </c>
-      <c r="C99" s="54" t="s">
+      <c r="C99" s="51" t="s">
         <v>189</v>
       </c>
-      <c r="D99" s="30">
+      <c r="D99" s="29">
         <v>46</v>
       </c>
-      <c r="E99" s="31" t="str">
+      <c r="E99" s="29"/>
+      <c r="F99" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Full City</v>
       </c>
     </row>
-    <row r="100" spans="2:10" ht="21" customHeight="1">
-      <c r="B100" s="20">
+    <row r="100" spans="2:11" ht="21" customHeight="1">
+      <c r="B100" s="19">
         <v>107</v>
       </c>
-      <c r="C100" s="29" t="s">
+      <c r="C100" s="28" t="s">
         <v>190</v>
       </c>
-      <c r="D100" s="16">
+      <c r="D100" s="15">
         <f>D46</f>
         <v>47</v>
       </c>
-      <c r="E100" s="31" t="str">
+      <c r="F100" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Full City</v>
       </c>
-      <c r="J100" s="46" t="s">
+      <c r="K100" s="43" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="101" spans="2:10" ht="21" customHeight="1">
-      <c r="B101" s="20">
+    <row r="101" spans="2:11" ht="21" customHeight="1">
+      <c r="B101" s="19">
         <v>106</v>
       </c>
-      <c r="C101" s="29" t="s">
+      <c r="C101" s="28" t="s">
         <v>191</v>
       </c>
-      <c r="D101" s="16">
+      <c r="D101" s="15">
         <f>D51</f>
         <v>53</v>
       </c>
-      <c r="E101" s="31" t="str">
+      <c r="F101" s="30" t="str">
         <f t="shared" si="2"/>
         <v>City</v>
       </c>
-      <c r="J101" s="46" t="s">
+      <c r="K101" s="43" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="102" spans="2:10" ht="21" customHeight="1">
-      <c r="B102" s="20">
+    <row r="102" spans="2:11" ht="21" customHeight="1">
+      <c r="B102" s="19">
         <v>98</v>
       </c>
-      <c r="C102" s="29" t="s">
+      <c r="C102" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="D102" s="30">
+      <c r="D102" s="29">
         <v>54</v>
       </c>
-      <c r="E102" s="31" t="str">
+      <c r="E102" s="29"/>
+      <c r="F102" s="30" t="str">
         <f t="shared" si="2"/>
         <v>City</v>
       </c>
-      <c r="F102" s="19" t="s">
+      <c r="G102" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="G102" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H102" s="19" t="s">
+      <c r="H102" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I102" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="I102" s="19">
+      <c r="J102" s="18">
         <v>225</v>
       </c>
     </row>
-    <row r="103" spans="2:10" ht="21" customHeight="1">
-      <c r="B103" s="20">
+    <row r="103" spans="2:11" ht="21" customHeight="1">
+      <c r="B103" s="19">
         <v>99</v>
       </c>
-      <c r="C103" s="29" t="s">
+      <c r="C103" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="D103" s="30">
+      <c r="D103" s="29">
         <v>59</v>
       </c>
-      <c r="E103" s="31" t="str">
+      <c r="E103" s="29"/>
+      <c r="F103" s="30" t="str">
         <f t="shared" si="2"/>
         <v>City</v>
       </c>
-      <c r="F103" s="19" t="s">
+      <c r="G103" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="G103" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H103" s="19" t="s">
+      <c r="H103" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I103" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="I103" s="19">
+      <c r="J103" s="18">
         <v>229</v>
       </c>
-      <c r="J103" s="46" t="s">
+      <c r="K103" s="43" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="104" spans="2:10" ht="21" customHeight="1">
-      <c r="B104" s="20">
+    <row r="104" spans="2:11" ht="21" customHeight="1">
+      <c r="B104" s="19">
         <v>100</v>
       </c>
-      <c r="C104" s="29" t="s">
+      <c r="C104" s="28" t="s">
         <v>196</v>
       </c>
-      <c r="D104" s="30">
+      <c r="D104" s="29">
         <v>81</v>
       </c>
-      <c r="E104" s="31" t="str">
+      <c r="E104" s="29"/>
+      <c r="F104" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Cinnamon</v>
       </c>
     </row>
-    <row r="105" spans="2:10" ht="21" customHeight="1">
-      <c r="B105" s="20">
+    <row r="105" spans="2:11" ht="21" customHeight="1">
+      <c r="B105" s="19">
         <v>101</v>
       </c>
-      <c r="C105" s="29" t="s">
+      <c r="C105" s="28" t="s">
         <v>197</v>
       </c>
-      <c r="D105" s="30">
+      <c r="D105" s="29">
         <v>56</v>
       </c>
-      <c r="E105" s="31" t="str">
+      <c r="E105" s="29"/>
+      <c r="F105" s="30" t="str">
         <f t="shared" si="2"/>
         <v>City</v>
       </c>
     </row>
-    <row r="106" spans="2:10" ht="21" customHeight="1">
-      <c r="B106" s="20">
+    <row r="106" spans="2:11" ht="21" customHeight="1">
+      <c r="B106" s="19">
         <v>102</v>
       </c>
-      <c r="C106" s="29" t="s">
+      <c r="C106" s="28" t="s">
         <v>198</v>
       </c>
-      <c r="D106" s="30">
+      <c r="D106" s="29">
         <v>50</v>
       </c>
-      <c r="E106" s="31" t="str">
+      <c r="E106" s="29"/>
+      <c r="F106" s="30" t="str">
         <f t="shared" si="2"/>
         <v>City</v>
       </c>
     </row>
-    <row r="107" spans="2:10" ht="21" customHeight="1">
-      <c r="B107" s="20">
+    <row r="107" spans="2:11" ht="21" customHeight="1">
+      <c r="B107" s="19">
         <v>103</v>
       </c>
-      <c r="C107" s="29" t="s">
+      <c r="C107" s="28" t="s">
         <v>199</v>
       </c>
-      <c r="D107" s="30">
+      <c r="D107" s="29">
         <v>60</v>
       </c>
-      <c r="E107" s="31" t="str">
+      <c r="E107" s="29"/>
+      <c r="F107" s="30" t="str">
         <f t="shared" si="2"/>
         <v>High</v>
       </c>
     </row>
-    <row r="108" spans="2:10" ht="21" customHeight="1">
-      <c r="B108" s="55">
+    <row r="108" spans="2:11" ht="21" customHeight="1">
+      <c r="B108" s="52">
         <v>104</v>
       </c>
-      <c r="C108" s="29" t="s">
+      <c r="C108" s="28" t="s">
         <v>200</v>
       </c>
-      <c r="D108" s="30">
+      <c r="D108" s="29">
         <v>56</v>
       </c>
-      <c r="E108" s="31" t="str">
+      <c r="E108" s="29"/>
+      <c r="F108" s="30" t="str">
         <f t="shared" si="2"/>
         <v>City</v>
       </c>
     </row>
-    <row r="109" spans="2:10" ht="21" customHeight="1">
-      <c r="B109" s="55">
+    <row r="109" spans="2:11" ht="21" customHeight="1">
+      <c r="B109" s="52">
         <v>105</v>
       </c>
-      <c r="C109" s="29" t="s">
+      <c r="C109" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="D109" s="30">
+      <c r="D109" s="29">
         <v>53</v>
       </c>
-      <c r="E109" s="31" t="str">
+      <c r="E109" s="29"/>
+      <c r="F109" s="30" t="str">
         <f t="shared" si="2"/>
         <v>City</v>
       </c>
     </row>
-    <row r="110" spans="2:10" ht="21" customHeight="1">
-      <c r="B110" s="55">
+    <row r="110" spans="2:11" ht="21" customHeight="1">
+      <c r="B110" s="52">
         <v>108</v>
       </c>
-      <c r="C110" s="29" t="s">
+      <c r="C110" s="28" t="s">
         <v>202</v>
       </c>
-      <c r="D110" s="16">
+      <c r="D110" s="15">
         <v>50</v>
       </c>
-      <c r="E110" s="31" t="str">
+      <c r="F110" s="30" t="str">
         <f t="shared" si="2"/>
         <v>City</v>
       </c>
-      <c r="J110" s="46" t="s">
+      <c r="K110" s="43" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="111" spans="2:10" ht="21" customHeight="1">
-      <c r="B111" s="55">
+    <row r="111" spans="2:11" ht="21" customHeight="1">
+      <c r="B111" s="52">
         <v>109</v>
       </c>
-      <c r="E111" s="31" t="str">
+      <c r="F111" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="112" spans="2:10" ht="21" customHeight="1">
-      <c r="B112" s="55">
+    <row r="112" spans="2:11" ht="21" customHeight="1">
+      <c r="B112" s="52">
         <v>110</v>
       </c>
-      <c r="E112" s="31" t="str">
+      <c r="F112" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="113" spans="2:5" ht="21" customHeight="1">
-      <c r="B113" s="55">
+    <row r="113" spans="2:6" ht="21" customHeight="1">
+      <c r="B113" s="52">
         <v>111</v>
       </c>
-      <c r="E113" s="31" t="str">
+      <c r="F113" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="114" spans="2:5" ht="21" customHeight="1">
-      <c r="B114" s="55">
+    <row r="114" spans="2:6" ht="21" customHeight="1">
+      <c r="B114" s="52">
         <v>112</v>
       </c>
-      <c r="E114" s="31" t="str">
+      <c r="F114" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="115" spans="2:5" ht="21" customHeight="1">
-      <c r="B115" s="55">
+    <row r="115" spans="2:6" ht="21" customHeight="1">
+      <c r="B115" s="52">
         <v>113</v>
       </c>
-      <c r="E115" s="31" t="str">
+      <c r="F115" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="116" spans="2:5" ht="21" customHeight="1">
-      <c r="B116" s="55">
+    <row r="116" spans="2:6" ht="21" customHeight="1">
+      <c r="B116" s="52">
         <v>114</v>
       </c>
-      <c r="E116" s="31" t="str">
+      <c r="F116" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="117" spans="2:5" ht="21" customHeight="1">
-      <c r="B117" s="55">
+    <row r="117" spans="2:6" ht="21" customHeight="1">
+      <c r="B117" s="52">
         <v>115</v>
       </c>
-      <c r="E117" s="31" t="str">
+      <c r="F117" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="118" spans="2:5" ht="21" customHeight="1">
-      <c r="B118" s="55">
+    <row r="118" spans="2:6" ht="21" customHeight="1">
+      <c r="B118" s="52">
         <v>116</v>
       </c>
-      <c r="E118" s="31" t="str">
+      <c r="F118" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="119" spans="2:5" ht="21" customHeight="1">
-      <c r="B119" s="55">
+    <row r="119" spans="2:6" ht="21" customHeight="1">
+      <c r="B119" s="52">
         <v>117</v>
       </c>
-      <c r="E119" s="31" t="str">
+      <c r="F119" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="120" spans="2:5" ht="21" customHeight="1">
-      <c r="B120" s="55">
+    <row r="120" spans="2:6" ht="21" customHeight="1">
+      <c r="B120" s="52">
         <v>118</v>
       </c>
-      <c r="E120" s="31" t="str">
+      <c r="F120" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="121" spans="2:5" ht="21" customHeight="1">
-      <c r="B121" s="55">
+    <row r="121" spans="2:6" ht="21" customHeight="1">
+      <c r="B121" s="52">
         <v>119</v>
       </c>
-      <c r="E121" s="31" t="str">
+      <c r="F121" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="122" spans="2:5" ht="21" customHeight="1">
-      <c r="B122" s="55">
+    <row r="122" spans="2:6" ht="21" customHeight="1">
+      <c r="B122" s="52">
         <v>120</v>
       </c>
-      <c r="E122" s="31" t="str">
+      <c r="F122" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="123" spans="2:5" ht="21" customHeight="1">
-      <c r="B123" s="55">
+    <row r="123" spans="2:6" ht="21" customHeight="1">
+      <c r="B123" s="52">
         <v>121</v>
       </c>
-      <c r="E123" s="31" t="str">
+      <c r="F123" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="124" spans="2:5" ht="21" customHeight="1">
-      <c r="B124" s="55">
+    <row r="124" spans="2:6" ht="21" customHeight="1">
+      <c r="B124" s="52">
         <v>122</v>
       </c>
-      <c r="E124" s="31" t="str">
+      <c r="F124" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="125" spans="2:5" ht="21" customHeight="1">
-      <c r="B125" s="55">
+    <row r="125" spans="2:6" ht="21" customHeight="1">
+      <c r="B125" s="52">
         <v>123</v>
       </c>
-      <c r="E125" s="31" t="str">
+      <c r="F125" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="126" spans="2:5" ht="21" customHeight="1">
-      <c r="B126" s="55">
+    <row r="126" spans="2:6" ht="21" customHeight="1">
+      <c r="B126" s="52">
         <v>124</v>
       </c>
-      <c r="E126" s="31" t="str">
+      <c r="F126" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="127" spans="2:5" ht="21" customHeight="1">
-      <c r="B127" s="55">
+    <row r="127" spans="2:6" ht="21" customHeight="1">
+      <c r="B127" s="52">
         <v>125</v>
       </c>
-      <c r="E127" s="31" t="str">
+      <c r="F127" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="128" spans="2:5" ht="21" customHeight="1">
-      <c r="B128" s="55">
+    <row r="128" spans="2:6" ht="21" customHeight="1">
+      <c r="B128" s="52">
         <v>126</v>
       </c>
-      <c r="E128" s="31" t="str">
+      <c r="F128" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="129" spans="2:5" ht="21" customHeight="1">
-      <c r="B129" s="55">
+    <row r="129" spans="2:6" ht="21" customHeight="1">
+      <c r="B129" s="52">
         <v>127</v>
       </c>
-      <c r="E129" s="31" t="str">
+      <c r="F129" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="130" spans="2:5" ht="21" customHeight="1">
-      <c r="B130" s="55">
+    <row r="130" spans="2:6" ht="21" customHeight="1">
+      <c r="B130" s="52">
         <v>128</v>
       </c>
-      <c r="E130" s="31" t="str">
+      <c r="F130" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="131" spans="2:5" ht="21" customHeight="1">
-      <c r="B131" s="55">
+    <row r="131" spans="2:6" ht="21" customHeight="1">
+      <c r="B131" s="52">
         <v>129</v>
       </c>
-      <c r="E131" s="31" t="str">
-        <f t="shared" ref="E131:E152" si="3">IF(D131&gt;=90, "Light",
+      <c r="F131" s="30" t="str">
+        <f t="shared" ref="F131:F152" si="3">IF(D131&gt;=90, "Light",
  IF(D131&gt;=80, "Cinnamon",
  IF(D131&gt;=70, "Medium",
  IF(D131&gt;=60, "High",
@@ -4966,203 +5075,203 @@
         <v>Italian</v>
       </c>
     </row>
-    <row r="132" spans="2:5" ht="21" customHeight="1">
-      <c r="B132" s="55">
+    <row r="132" spans="2:6" ht="21" customHeight="1">
+      <c r="B132" s="52">
         <v>130</v>
       </c>
-      <c r="E132" s="31" t="str">
+      <c r="F132" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="133" spans="2:5" ht="21" customHeight="1">
-      <c r="B133" s="55">
+    <row r="133" spans="2:6" ht="21" customHeight="1">
+      <c r="B133" s="52">
         <v>131</v>
       </c>
-      <c r="E133" s="31" t="str">
+      <c r="F133" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="134" spans="2:5" ht="21" customHeight="1">
-      <c r="B134" s="55">
+    <row r="134" spans="2:6" ht="21" customHeight="1">
+      <c r="B134" s="52">
         <v>132</v>
       </c>
-      <c r="E134" s="31" t="str">
+      <c r="F134" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="135" spans="2:5" ht="21" customHeight="1">
-      <c r="B135" s="55">
+    <row r="135" spans="2:6" ht="21" customHeight="1">
+      <c r="B135" s="52">
         <v>133</v>
       </c>
-      <c r="E135" s="31" t="str">
+      <c r="F135" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="136" spans="2:5" ht="21" customHeight="1">
-      <c r="B136" s="55">
+    <row r="136" spans="2:6" ht="21" customHeight="1">
+      <c r="B136" s="52">
         <v>134</v>
       </c>
-      <c r="E136" s="31" t="str">
+      <c r="F136" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="137" spans="2:5" ht="21" customHeight="1">
-      <c r="B137" s="55">
+    <row r="137" spans="2:6" ht="21" customHeight="1">
+      <c r="B137" s="52">
         <v>135</v>
       </c>
-      <c r="E137" s="31" t="str">
+      <c r="F137" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="138" spans="2:5" ht="21" customHeight="1">
-      <c r="B138" s="55">
+    <row r="138" spans="2:6" ht="21" customHeight="1">
+      <c r="B138" s="52">
         <v>136</v>
       </c>
-      <c r="E138" s="31" t="str">
+      <c r="F138" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="139" spans="2:5" ht="21" customHeight="1">
-      <c r="B139" s="55">
+    <row r="139" spans="2:6" ht="21" customHeight="1">
+      <c r="B139" s="52">
         <v>137</v>
       </c>
-      <c r="E139" s="31" t="str">
+      <c r="F139" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="140" spans="2:5" ht="21" customHeight="1">
-      <c r="B140" s="55">
+    <row r="140" spans="2:6" ht="21" customHeight="1">
+      <c r="B140" s="52">
         <v>138</v>
       </c>
-      <c r="E140" s="31" t="str">
+      <c r="F140" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="141" spans="2:5" ht="21" customHeight="1">
-      <c r="B141" s="55">
+    <row r="141" spans="2:6" ht="21" customHeight="1">
+      <c r="B141" s="52">
         <v>139</v>
       </c>
-      <c r="E141" s="31" t="str">
+      <c r="F141" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="142" spans="2:5" ht="21" customHeight="1">
-      <c r="B142" s="55">
+    <row r="142" spans="2:6" ht="21" customHeight="1">
+      <c r="B142" s="52">
         <v>140</v>
       </c>
-      <c r="E142" s="31" t="str">
+      <c r="F142" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="143" spans="2:5" ht="21" customHeight="1">
-      <c r="B143" s="55">
+    <row r="143" spans="2:6" ht="21" customHeight="1">
+      <c r="B143" s="52">
         <v>141</v>
       </c>
-      <c r="E143" s="31" t="str">
+      <c r="F143" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="144" spans="2:5" ht="21" customHeight="1">
-      <c r="B144" s="55">
+    <row r="144" spans="2:6" ht="21" customHeight="1">
+      <c r="B144" s="52">
         <v>142</v>
       </c>
-      <c r="E144" s="31" t="str">
+      <c r="F144" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="145" spans="2:5" ht="21" customHeight="1">
-      <c r="B145" s="55">
+    <row r="145" spans="2:6" ht="21" customHeight="1">
+      <c r="B145" s="52">
         <v>143</v>
       </c>
-      <c r="E145" s="31" t="str">
+      <c r="F145" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="146" spans="2:5" ht="21" customHeight="1">
-      <c r="B146" s="55">
+    <row r="146" spans="2:6" ht="21" customHeight="1">
+      <c r="B146" s="52">
         <v>144</v>
       </c>
-      <c r="E146" s="31" t="str">
+      <c r="F146" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="147" spans="2:5" ht="21" customHeight="1">
-      <c r="B147" s="55">
+    <row r="147" spans="2:6" ht="21" customHeight="1">
+      <c r="B147" s="52">
         <v>145</v>
       </c>
-      <c r="E147" s="31" t="str">
+      <c r="F147" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="148" spans="2:5" ht="21" customHeight="1">
-      <c r="B148" s="55">
+    <row r="148" spans="2:6" ht="21" customHeight="1">
+      <c r="B148" s="52">
         <v>146</v>
       </c>
-      <c r="E148" s="31" t="str">
+      <c r="F148" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="149" spans="2:5" ht="21" customHeight="1">
-      <c r="B149" s="55">
+    <row r="149" spans="2:6" ht="21" customHeight="1">
+      <c r="B149" s="52">
         <v>147</v>
       </c>
-      <c r="E149" s="31" t="str">
+      <c r="F149" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="150" spans="2:5" ht="21" customHeight="1">
-      <c r="B150" s="55">
+    <row r="150" spans="2:6" ht="21" customHeight="1">
+      <c r="B150" s="52">
         <v>148</v>
       </c>
-      <c r="E150" s="31" t="str">
+      <c r="F150" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="151" spans="2:5" ht="21" customHeight="1">
-      <c r="B151" s="55">
+    <row r="151" spans="2:6" ht="21" customHeight="1">
+      <c r="B151" s="52">
         <v>149</v>
       </c>
-      <c r="E151" s="31" t="str">
+      <c r="F151" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="152" spans="2:5" ht="21" customHeight="1">
-      <c r="B152" s="55">
+    <row r="152" spans="2:6" ht="21" customHeight="1">
+      <c r="B152" s="52">
         <v>150</v>
       </c>
-      <c r="E152" s="31" t="str">
+      <c r="F152" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Italian</v>
       </c>
     </row>
-    <row r="153" spans="2:5" ht="21" customHeight="1"/>
-    <row r="154" spans="2:5" ht="21" customHeight="1"/>
-    <row r="155" spans="2:5" ht="21" customHeight="1"/>
-    <row r="156" spans="2:5" ht="21" customHeight="1"/>
-    <row r="157" spans="2:5" ht="21" customHeight="1"/>
-    <row r="158" spans="2:5" ht="21" customHeight="1"/>
-    <row r="159" spans="2:5" ht="21" customHeight="1"/>
-    <row r="160" spans="2:5" ht="21" customHeight="1"/>
+    <row r="153" spans="2:6" ht="21" customHeight="1"/>
+    <row r="154" spans="2:6" ht="21" customHeight="1"/>
+    <row r="155" spans="2:6" ht="21" customHeight="1"/>
+    <row r="156" spans="2:6" ht="21" customHeight="1"/>
+    <row r="157" spans="2:6" ht="21" customHeight="1"/>
+    <row r="158" spans="2:6" ht="21" customHeight="1"/>
+    <row r="159" spans="2:6" ht="21" customHeight="1"/>
+    <row r="160" spans="2:6" ht="21" customHeight="1"/>
     <row r="161" ht="21" customHeight="1"/>
     <row r="162" ht="21" customHeight="1"/>
     <row r="163" ht="21" customHeight="1"/>
@@ -5323,31 +5432,31 @@
     <row r="318" ht="21" customHeight="1"/>
     <row r="319" ht="21" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="B2:J107">
-    <filterColumn colId="4" showButton="0"/>
+  <autoFilter ref="B2:K107">
     <filterColumn colId="5" showButton="0"/>
+    <filterColumn colId="6" showButton="0"/>
     <sortState ref="B3:J152">
       <sortCondition ref="C2:C107"/>
     </sortState>
   </autoFilter>
   <mergeCells count="2">
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="P10:Q10"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="C2:D1048576">
+  <conditionalFormatting sqref="C2:E1048576">
     <cfRule type="notContainsBlanks" dxfId="10" priority="10">
       <formula>LEN(TRIM(C2))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1">
+  <conditionalFormatting sqref="D1:E1">
     <cfRule type="notContainsBlanks" dxfId="9" priority="11">
       <formula>LEN(TRIM(D1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M1 L2:M3 M4:M7">
+  <conditionalFormatting sqref="N1 M2:N3 N4:N7">
     <cfRule type="notContainsBlanks" dxfId="8" priority="9">
-      <formula>LEN(TRIM(L1))&gt;0</formula>
+      <formula>LEN(TRIM(M1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5357,8 +5466,8 @@
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="1" operator="containsText" id="{FFBBEA22-3CB5-4D4A-9E30-2D2FFBBB7101}">
-            <xm:f>NOT(ISERROR(SEARCH($P$9,E1)))</xm:f>
-            <xm:f>$P$9</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH($Q$9,F1)))</xm:f>
+            <xm:f>$Q$9</xm:f>
             <x14:dxf>
               <font>
                 <color theme="0"/>
@@ -5371,8 +5480,8 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="containsText" priority="2" operator="containsText" id="{8A4A4E54-D1C1-4C81-9125-BD04AF7A69FC}">
-            <xm:f>NOT(ISERROR(SEARCH($P$8,E1)))</xm:f>
-            <xm:f>$P$8</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH($Q$8,F1)))</xm:f>
+            <xm:f>$Q$8</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -5382,8 +5491,8 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="containsText" priority="3" operator="containsText" id="{2DCBD48B-C102-4827-8E01-19391C7658A5}">
-            <xm:f>NOT(ISERROR(SEARCH($P$7,E1)))</xm:f>
-            <xm:f>$P$7</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH($Q$7,F1)))</xm:f>
+            <xm:f>$Q$7</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -5393,8 +5502,8 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="containsText" priority="4" operator="containsText" id="{33A2AB65-CFDE-4914-AEA3-54E2A6E616D6}">
-            <xm:f>NOT(ISERROR(SEARCH($P$6,E1)))</xm:f>
-            <xm:f>$P$6</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH($Q$6,F1)))</xm:f>
+            <xm:f>$Q$6</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -5404,8 +5513,8 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="containsText" priority="5" operator="containsText" id="{48ED215F-AB44-450A-B638-D765FA9AEC0E}">
-            <xm:f>NOT(ISERROR(SEARCH($P$5,E1)))</xm:f>
-            <xm:f>$P$5</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH($Q$5,F1)))</xm:f>
+            <xm:f>$Q$5</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -5415,8 +5524,8 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="containsText" priority="6" operator="containsText" id="{749E6BB5-4A82-41C4-9DA9-8B5E50937DB7}">
-            <xm:f>NOT(ISERROR(SEARCH($P$4,E1)))</xm:f>
-            <xm:f>$P$4</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH($Q$4,F1)))</xm:f>
+            <xm:f>$Q$4</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -5426,8 +5535,8 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="containsText" priority="7" operator="containsText" id="{3B931EE2-50AC-4277-9484-5018BA3F9883}">
-            <xm:f>NOT(ISERROR(SEARCH($P$3,E1)))</xm:f>
-            <xm:f>$P$3</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH($Q$3,F1)))</xm:f>
+            <xm:f>$Q$3</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -5437,8 +5546,8 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="containsText" priority="8" operator="containsText" id="{5D68607D-0D52-4B3B-A787-D7AEE198B35C}">
-            <xm:f>NOT(ISERROR(SEARCH($P$2,E1)))</xm:f>
-            <xm:f>$P$2</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH($Q$2,F1)))</xm:f>
+            <xm:f>$Q$2</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -5447,7 +5556,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>E1:E1048576</xm:sqref>
+          <xm:sqref>F1:F1048576</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
